--- a/HPTS_results.xlsx
+++ b/HPTS_results.xlsx
@@ -23,7 +23,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 13" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 14" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 15" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reproduction check" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table A1" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table A2" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table A3" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table A4" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table A5" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reproduction check" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -764,13 +769,73 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Table A1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Table A1. Variable definitions for the distributed dataset.</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>Table A2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Table A2. Data and leakage audit of the model-ready panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Table A3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Table A3. Validation MSE for the panel models across the penalty lambda and the pooling multiplier p.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Table A4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Table A4. Validation MSE for the per-asset models across the penalty lambda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Table A5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Table A5. Symmetry-breaking ratio by predictor block and refit date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>Reproduction check</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Written by HPTS_reproduce.ipynb: recomputed values next to published values.</t>
         </is>
@@ -2919,400 +2984,1369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Headline comparisons against published values</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Comparison</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Gain (%)</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>NW t</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Published gain (%)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>Published NW t</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>Match</t>
+          <t>Table A1. Variable definitions for the distributed dataset.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HPTS_Final vs HAR</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="D3" t="n">
-        <v>6.99</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Definition</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HPTS_NoIV vs HAR</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>UTC forecast origin; every row uses information observable at this time</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HPTS_Final vs HPTS_NoIV</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Cryptocurrency USDT pair</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HPTS_Final vs HAR, 15 assets without options</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="D6" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>split</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>train (before 2023), validation (2023) or holdout (2024 onward)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Log realised variance over the next exact 24 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>y_3d, y_7d</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Log realised variance over the next exact 72 h and 168 h</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Table 6  -  symmetry breaking by predictor block</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ret_24</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Trailing 24 h log spot return; used by the GARCH baselines</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Block</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Mean absolute common slope</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Deviation RMS</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Total RMS</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Ratio</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>c_logrv_6, c_logrv_24, c_logrv_72, c_logrv_168</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>HAR</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Trailing log realised variance over 6, 24, 72 and 168 h</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HAR</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.1209</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.1305</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0794</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>log_dvol_open</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Log of the current UTC day's BTC DVOL opening value</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>dvol_chg_1_open, dvol_chg_5_open</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>IV</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0.0708</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0108</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0859</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.153</v>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>One- and five-day changes in BTC DVOL open</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>iv_rv_gap_open</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>BTC implied variance minus trailing realised variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>log_dvol_eth_open</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Log of the current UTC day's ETH DVOL opening value</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>dvol_eth_chg_1_open</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>One-day change in ETH DVOL open</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>iv_spread_open</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>BTC minus ETH implied volatility; rejected at validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>c_xs_logrv24</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Cross-sectional mean log realised variance over 24 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>c_xs_logrv24_rank</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Rank of the asset within that cross-section</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>c_xs_dispersion</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Cross-sectional dispersion of log realised variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>c_xs_breadth</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Share of assets with positive trailing 24 h return</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>c_beta_mkt_168</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Beta on the equally weighted market over 168 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>c_corr_mkt_168</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Correlation with the market over 168 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>c_resid_ret_24</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Trailing 24 h return orthogonal to the market</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>c_mkt_ret_24</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Trailing 24 h market return</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>c_signed_jump_24</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>TAIL</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.0529</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.0123</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0629</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.2323</v>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Signed jump variation over 24 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>c_jump_asym_24</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Asymmetry between upside and downside jump variation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>c_jump_share_24</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Jump share of total realised variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>c_vol_ratio_6_72, c_vol_ratio_24_168</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Short- to long-horizon realised-variance ratios</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>c_path_eff_24</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Path efficiency: net move divided by total absolute movement</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>c_range_rel</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>High-low range relative to the closing price</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>c_amihud_24</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Amihud illiquidity over 24 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Every predictor is constructed from information available at the forecast origin. Column names match model_data.csv in the archived repository.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Table A2. Data and leakage audit of the model-ready panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Target definition</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>log(sum of squared hourly log returns) over the next exact 24 h</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Row count</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>31,965</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Asset count</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>First origin</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2021-03-29</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Last origin</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Missing model values</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Duplicate asset-dates</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Same-day DVOL close, high or low fields</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Model data SHA-256</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>e801ea0df38a6e2784fc58677c098f89a44f734f305a451500d3ff1ccde6ccee</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Audit executed on the distributed model file before any estimation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Table A3. Validation MSE for the panel models across the penalty lambda and the pooling multiplier p.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>lambda</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>p = 1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>p = 3</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>p = 10</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>p = 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Full fixed effects</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>0.7124</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>0.7123</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.7120</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.7110</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>HPTS-NoIV</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>0.7367</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>0.7361</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>0.7353</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>0.7348</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0.7362</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>0.7355</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>0.7349</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>0.7346</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>0.7359</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>0.7355</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>0.7351</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>0.7351</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>0.7369</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>0.7366</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>0.7367</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>0.7376</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>HPTS-CommonIV</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>0.7107</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>0.7101</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>0.7092</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>0.7088</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0.7099</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>0.7092</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>0.7087</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>0.7084</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>XSEC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.0396</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.0109</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.0529</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.2746</v>
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0.7090</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>0.7086</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>0.7081</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>0.7079</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>0.7079</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>0.7074</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>0.7071</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>0.7077</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>HPTS-IVSpecific</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0.7132</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.7128</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0.7119</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0.7107</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Table 7  -  validation along the pooling path</t>
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.7126</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.7118</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.7105</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>0.7089</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Configuration</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Validation MSE</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Symmetry status</t>
+      <c r="A18" s="5" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>0.7114</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>0.7102</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>0.7086</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>0.7076</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Full fixed effects</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Exact common slopes</t>
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>0.7090</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>0.7076</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>0.7066</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>0.7076</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>HPTS-Final</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7106</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Weakly restricted</t>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>0.7194</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>0.7177</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>0.7147</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>0.7119</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>HPTS-Final</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.7077</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Restricted</t>
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0.7174</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>0.7147</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>0.7115</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>0.7087</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HPTS-Final</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>10</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.7056</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Selected</t>
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>0.7145</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>0.7116</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>0.7084</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>0.7064</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>HPTS-Final</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>30</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.7059</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Strongly restricted</t>
+      <c r="A23" s="7" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>0.7106</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>0.7077</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>0.7056</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>0.7059</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Full per-asset ridge</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.6984</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Unrestricted</t>
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Validation MSE on calendar 2023. Full fixed effects admits no asset-specific deviations, so p does not apply. The selected configuration is HPTS-Final at lambda = 100, p = 10.</t>
         </is>
       </c>
     </row>
@@ -3431,6 +4465,1078 @@
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>All option variables use the current UTC day's DVOL opening value only. The BTC-ETH spread is excluded from the final specification because it raised validation MSE.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Table A4. Validation MSE for the per-asset models across the penalty lambda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>lambda = 0.1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>lambda = 1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>lambda = 10</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>lambda = 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>HAR</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>0.7743</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>0.7745</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>0.7761</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>0.7904</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>HAR with jumps</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>0.7718</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>0.7719</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>0.7737</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0.7885</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>HAR + IV per asset</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.7417</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.7414</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.7383</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.7271</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Full per-asset ridge</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>0.7207</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>0.7201</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>0.7156</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>0.6984</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Validation MSE on calendar 2023 for the separately estimated per-asset models. Selected values are shown in bold in Table 2's source metadata; the minimum in each row is the retained setting.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Table A5. Symmetry-breaking ratio by predictor block and refit date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Refit cutoff</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>HAR</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>0.071</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>0.123</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>0.233</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>0.285</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>0.129</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>0.236</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.134</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.246</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.282</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.076</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.236</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>0.147</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>0.231</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>0.149</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>0.225</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>0.319</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2024-12-26</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>0.073</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>0.227</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>0.076</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>0.159</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>0.225</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>0.311</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>0.076</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>0.155</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>0.222</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>0.301</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>0.276</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>0.084</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0.164</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>0.226</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>0.263</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>0.085</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>0.166</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>0.228</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.088</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0.171</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.227</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0.246</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.089</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0.171</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0.239</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0.243</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>0.089</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>0.171</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>0.245</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>0.247</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>0.168</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>0.241</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Ratio of asset-specific deviation RMS to mean absolute common slope, by predictor block and refit date. Averages over these 16 refits give Table 6.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Headline comparisons against published values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Gain (%)</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>NW t</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Published gain (%)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Published NW t</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HPTS_Final vs HAR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HPTS_NoIV vs HAR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HPTS_Final vs HPTS_NoIV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HPTS_Final vs HAR, 15 assets without options</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Table 6  -  symmetry breaking by predictor block</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Mean absolute common slope</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Deviation RMS</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Total RMS</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HAR</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0794</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0859</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TAIL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2323</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>XSEC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2746</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Table 7  -  validation along the pooling path</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Validation MSE</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Symmetry status</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Full fixed effects</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Exact common slopes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HPTS-Final</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7106</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Weakly restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HPTS-Final</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7077</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HPTS-Final</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7056</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HPTS-Final</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7059</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Strongly restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Full per-asset ridge</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6984</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Unrestricted</t>
         </is>
       </c>
     </row>
@@ -4053,27 +6159,27 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>1.4779</t>
+          <t>0.6212</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>-149.78</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>2.10 x 10-52</t>
+          <t>2.66 x 10-13</t>
         </is>
       </c>
     </row>
@@ -4144,7 +6250,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Each time-series forecast is mapped to the target scale by a calendar-2023 regression that is then frozen for the holdout. The HPTS row reports its own gain over HAR on this common subsample.</t>
+          <t>Each time-series forecast is mapped to the target scale by a calendar-2023 regression that is then frozen for the holdout. The HPTS row reports its own gain over HAR on this common subsample. The fractional filter uses the Geweke-Porter-Hudak estimate of d with a fixed truncation lag of 200.</t>
         </is>
       </c>
     </row>
@@ -4785,7 +6891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4793,6 +6899,8 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4810,7 +6918,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Mean absolute common slope</t>
+          <t>Common slope</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -4825,7 +6933,17 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Total RMS</t>
+          <t>Null mean</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Null 95% interval</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>p</t>
         </is>
       </c>
     </row>
@@ -4847,12 +6965,22 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.0795</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>0.1297</t>
+          <t>0.0388</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>[0.032, 0.045]</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>0.005</t>
         </is>
       </c>
     </row>
@@ -4874,12 +7002,22 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1537</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>0.0854</t>
+          <t>0.0891</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>[0.078, 0.103]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>0.005</t>
         </is>
       </c>
     </row>
@@ -4901,12 +7039,22 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2325</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>0.0626</t>
+          <t>0.1983</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>[0.178, 0.219]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>0.010</t>
         </is>
       </c>
     </row>
@@ -4928,19 +7076,29 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.2781</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>0.0526</t>
+          <t>0.1633</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>[0.146, 0.184]</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>0.005</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Averages over expanding-window refits of HPTS-Final. Ratio is deviation RMS divided by mean absolute common slope: 0 denotes exact exchangeability across assets, larger values denote greater symmetry breaking.</t>
+          <t>Coefficients are on standardised predictors and averaged across the 16 holdout refits. The ratio is the asset-specific deviation RMS relative to the mean absolute common slope, computed at each refit and then averaged, so it differs slightly from the ratio of the two preceding columns. The null is generated by permuting asset labels within each date and refitting, 200 draws at seed 77; p is the one-sided empirical probability of a ratio at least as large under that null.</t>
         </is>
       </c>
     </row>
